--- a/docs/webhook_v5_prometheus_rule_coverage.xlsx
+++ b/docs/webhook_v5_prometheus_rule_coverage.xlsx
@@ -43,7 +43,7 @@
       </c>
       <c r="B2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2026-05-09 15:38:13</t>
+          <t xml:space="preserve">2026-05-11 14:01:31</t>
         </is>
       </c>
     </row>

--- a/docs/webhook_v5_prometheus_rule_coverage.xlsx
+++ b/docs/webhook_v5_prometheus_rule_coverage.xlsx
@@ -43,7 +43,7 @@
       </c>
       <c r="B2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2026-05-11 14:01:31</t>
+          <t xml:space="preserve">2026-05-11 17:12:45</t>
         </is>
       </c>
     </row>

--- a/docs/webhook_v5_prometheus_rule_coverage.xlsx
+++ b/docs/webhook_v5_prometheus_rule_coverage.xlsx
@@ -43,7 +43,7 @@
       </c>
       <c r="B2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2026-05-11 17:12:45</t>
+          <t xml:space="preserve">2026-05-12 11:31:42</t>
         </is>
       </c>
     </row>

--- a/docs/webhook_v5_prometheus_rule_coverage.xlsx
+++ b/docs/webhook_v5_prometheus_rule_coverage.xlsx
@@ -43,7 +43,7 @@
       </c>
       <c r="B2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2026-05-12 11:31:42</t>
+          <t xml:space="preserve">2026-05-13 09:52:13</t>
         </is>
       </c>
     </row>
